--- a/sample-budget.xlsx
+++ b/sample-budget.xlsx
@@ -774,7 +774,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>🧘 Wellness</t>
+          <t>Wellness</t>
         </is>
       </c>
       <c r="B7" t="n">
